--- a/main/ig/StructureDefinition-dmi-supplydelivery-entete-livraison.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplydelivery-entete-livraison.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:37:28+00:00</t>
+    <t>2026-03-05T09:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-supplydelivery-entete-livraison.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplydelivery-entete-livraison.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T09:47:44+00:00</t>
+    <t>2026-03-05T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-supplydelivery-entete-livraison.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplydelivery-entete-livraison.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="261">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:00:25+00:00</t>
+    <t>2026-03-05T10:01:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -316,10 +316,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>SupplyDelivery.implicitRules</t>
   </si>
   <si>
@@ -339,6 +346,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>SupplyDelivery.language</t>
   </si>
   <si>
@@ -416,9 +426,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>SupplyDelivery.extension</t>
   </si>
   <si>
@@ -436,6 +443,9 @@
 </t>
   </si>
   <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
     <t>open</t>
   </si>
   <si>
@@ -462,10 +472,6 @@
     <t>Extension créée dans ce volet pour référencer l'organisation fabricant du DMI.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>SupplyDelivery.modifierExtension</t>
   </si>
   <si>
@@ -511,6 +517,9 @@
     <t>.id</t>
   </si>
   <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
     <t>SupplyDelivery.basedOn</t>
   </si>
   <si>
@@ -524,7 +533,14 @@
     <t>A plan, proposal or order that is fulfilled in whole or in part by this event.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -625,6 +641,9 @@
     <t>Indicates the type of dispensing event that is performed. Examples include: Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>The type of supply dispense.</t>
   </si>
   <si>
@@ -635,6 +654,9 @@
   </si>
   <si>
     <t>.code</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE</t>
   </si>
   <si>
     <t>SupplyDelivery.suppliedItem</t>
@@ -669,9 +691,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>SupplyDelivery.suppliedItem.extension</t>
   </si>
   <si>
@@ -714,7 +733,17 @@
     <t>The amount of supply that has been dispensed. Includes unit of measure.</t>
   </si>
   <si>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
+  </si>
+  <si>
     <t>.quantity</t>
+  </si>
+  <si>
+    <t>SN (see also Range) or CQ</t>
   </si>
   <si>
     <t>SupplyDelivery.suppliedItem.item[x]</t>
@@ -1136,7 +1165,7 @@
     <col min="26" max="26" width="43.90234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="30.5546875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1145,7 +1174,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="52.23046875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="27.45703125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="53.91015625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -1591,16 +1620,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -1611,10 +1640,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1637,16 +1666,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1696,7 +1725,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -1705,16 +1734,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -1725,10 +1754,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1751,16 +1780,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1786,13 +1815,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -1810,7 +1839,7 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -1819,16 +1848,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -1839,14 +1868,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -1865,16 +1894,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1924,7 +1953,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -1933,16 +1962,16 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -1953,14 +1982,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -1979,16 +2008,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2038,7 +2067,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2056,7 +2085,7 @@
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2067,10 +2096,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2093,13 +2122,13 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2138,17 +2167,19 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2157,10 +2188,10 @@
         <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2177,13 +2208,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>77</v>
@@ -2205,13 +2236,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2262,7 +2293,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2271,10 +2302,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2291,14 +2322,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2317,19 +2348,19 @@
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2366,19 +2397,19 @@
         <v>77</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2387,16 +2418,16 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2407,10 +2438,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2433,16 +2464,16 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2492,7 +2523,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2501,19 +2532,19 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>77</v>
@@ -2521,10 +2552,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2547,17 +2578,19 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O13" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -2606,7 +2639,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2615,19 +2648,19 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -2635,10 +2668,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2661,19 +2694,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -2722,7 +2755,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2731,19 +2764,19 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>77</v>
@@ -2751,10 +2784,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2777,16 +2810,16 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2812,31 +2845,31 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -2845,16 +2878,16 @@
         <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -2865,10 +2898,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2891,15 +2924,17 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -2948,7 +2983,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -2957,16 +2992,16 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -2977,10 +3012,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3003,15 +3038,17 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3036,31 +3073,31 @@
         <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="Z17" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3069,19 +3106,19 @@
         <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>77</v>
+        <v>205</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3089,10 +3126,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3115,13 +3152,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3172,7 +3209,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3181,16 +3218,16 @@
         <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3201,10 +3238,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3227,13 +3264,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3284,7 +3321,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3302,7 +3339,7 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>209</v>
+        <v>108</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3313,14 +3350,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3339,16 +3376,16 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3386,19 +3423,19 @@
         <v>77</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3407,16 +3444,16 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>209</v>
+        <v>101</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3427,14 +3464,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3453,19 +3490,19 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -3514,7 +3551,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3523,16 +3560,16 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3543,10 +3580,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3569,15 +3606,17 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3626,7 +3665,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3635,19 +3674,19 @@
         <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>230</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -3655,10 +3694,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3681,13 +3720,13 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3738,7 +3777,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3747,16 +3786,16 @@
         <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -3767,10 +3806,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3793,16 +3832,16 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3852,7 +3891,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -3861,30 +3900,30 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3907,15 +3946,17 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -3964,7 +4005,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -3973,16 +4014,16 @@
         <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -3993,10 +4034,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4019,15 +4060,17 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4076,7 +4119,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4085,16 +4128,16 @@
         <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4105,10 +4148,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4131,15 +4174,17 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4188,7 +4233,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4197,16 +4242,16 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-dmi-supplydelivery-entete-livraison.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplydelivery-entete-livraison.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="252">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:01:25+00:00</t>
+    <t>2026-03-05T10:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -316,162 +316,156 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>SupplyDelivery.implicitRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>SupplyDelivery.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>SupplyDelivery.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>SupplyDelivery.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>SupplyDelivery.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>SupplyDelivery.extension:ReferenceOrganisationInterne</t>
+  </si>
+  <si>
+    <t>ReferenceOrganisationInterne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tdmi/StructureDefinition/dmi-reference-organisation-interne}
+</t>
+  </si>
+  <si>
+    <t>DMI Reference Organisation Interne</t>
+  </si>
+  <si>
+    <t>Extension créée dans ce volet pour référencer l'organisation fabricant du DMI.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>SupplyDelivery.implicitRules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>SupplyDelivery.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>SupplyDelivery.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>SupplyDelivery.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>SupplyDelivery.extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>SupplyDelivery.extension:ReferenceOrganisationInterne</t>
-  </si>
-  <si>
-    <t>ReferenceOrganisationInterne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tdmi/StructureDefinition/dmi-reference-organisation-interne}
-</t>
-  </si>
-  <si>
-    <t>DMI Reference Organisation Interne</t>
-  </si>
-  <si>
-    <t>Extension créée dans ce volet pour référencer l'organisation fabricant du DMI.</t>
-  </si>
-  <si>
     <t>SupplyDelivery.modifierExtension</t>
   </si>
   <si>
@@ -517,9 +511,6 @@
     <t>.id</t>
   </si>
   <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
     <t>SupplyDelivery.basedOn</t>
   </si>
   <si>
@@ -533,14 +524,7 @@
     <t>A plan, proposal or order that is fulfilled in whole or in part by this event.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -641,9 +625,6 @@
     <t>Indicates the type of dispensing event that is performed. Examples include: Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>The type of supply dispense.</t>
   </si>
   <si>
@@ -654,9 +635,6 @@
   </si>
   <si>
     <t>.code</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
   </si>
   <si>
     <t>SupplyDelivery.suppliedItem</t>
@@ -691,6 +669,9 @@
     <t>Element.id</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>SupplyDelivery.suppliedItem.extension</t>
   </si>
   <si>
@@ -733,17 +714,7 @@
     <t>The amount of supply that has been dispensed. Includes unit of measure.</t>
   </si>
   <si>
-    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
     <t>.quantity</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
   </si>
   <si>
     <t>SupplyDelivery.suppliedItem.item[x]</t>
@@ -1165,7 +1136,7 @@
     <col min="26" max="26" width="43.90234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="30.5546875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1174,7 +1145,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="52.23046875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="53.91015625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="27.45703125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -1620,16 +1591,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -1640,10 +1611,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1666,16 +1637,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1725,7 +1696,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -1734,16 +1705,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ5" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -1754,10 +1725,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1780,16 +1751,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="L6" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1815,31 +1786,31 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="Y6" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -1848,16 +1819,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ6" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -1868,14 +1839,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -1894,16 +1865,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1953,7 +1924,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -1962,16 +1933,16 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -1982,14 +1953,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2008,16 +1979,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2067,7 +2038,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2085,7 +2056,7 @@
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2096,10 +2067,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2122,13 +2093,13 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2167,19 +2138,17 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AC9" s="2"/>
+      <c r="AD9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2188,10 +2157,10 @@
         <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2208,13 +2177,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>77</v>
@@ -2236,13 +2205,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2293,7 +2262,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2302,10 +2271,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2322,14 +2291,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2348,19 +2317,19 @@
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="O11" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2397,19 +2366,19 @@
         <v>77</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2418,16 +2387,16 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2438,10 +2407,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2464,16 +2433,16 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2523,7 +2492,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2532,19 +2501,19 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ12" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK12" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>77</v>
@@ -2552,10 +2521,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2578,19 +2547,17 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -2639,7 +2606,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2648,19 +2615,19 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ13" t="s" s="2">
-        <v>168</v>
-      </c>
       <c r="AK13" t="s" s="2">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -2668,10 +2635,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2694,19 +2661,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -2755,7 +2722,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2764,19 +2731,19 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ14" t="s" s="2">
-        <v>168</v>
-      </c>
       <c r="AK14" t="s" s="2">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>77</v>
@@ -2784,10 +2751,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2810,16 +2777,16 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2845,13 +2812,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -2869,7 +2836,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -2878,16 +2845,16 @@
         <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK15" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -2898,10 +2865,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2924,17 +2891,15 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -2983,7 +2948,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -2992,16 +2957,16 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ16" t="s" s="2">
-        <v>168</v>
-      </c>
       <c r="AK16" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3012,10 +2977,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3038,17 +3003,15 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3073,13 +3036,13 @@
         <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>77</v>
@@ -3097,7 +3060,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3106,19 +3069,19 @@
         <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ17" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK17" t="s" s="2">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>205</v>
+        <v>77</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3126,10 +3089,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3152,13 +3115,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3209,7 +3172,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3218,16 +3181,16 @@
         <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ18" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3238,10 +3201,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3264,13 +3227,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3321,7 +3284,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3339,7 +3302,7 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>108</v>
+        <v>209</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3350,14 +3313,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3376,16 +3339,16 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3423,19 +3386,19 @@
         <v>77</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3444,16 +3407,16 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3464,14 +3427,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3490,19 +3453,19 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -3551,7 +3514,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3560,16 +3523,16 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3580,10 +3543,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3606,17 +3569,15 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3665,7 +3626,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3674,19 +3635,19 @@
         <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ22" t="s" s="2">
-        <v>230</v>
-      </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -3694,10 +3655,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3720,13 +3681,13 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3777,7 +3738,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3786,16 +3747,16 @@
         <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ23" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -3806,10 +3767,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3832,16 +3793,16 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3891,7 +3852,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -3900,30 +3861,30 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ24" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK24" t="s" s="2">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3946,17 +3907,15 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4005,7 +3964,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4014,16 +3973,16 @@
         <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ25" t="s" s="2">
-        <v>168</v>
-      </c>
       <c r="AK25" t="s" s="2">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4034,10 +3993,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4060,17 +4019,15 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4119,7 +4076,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4128,16 +4085,16 @@
         <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ26" t="s" s="2">
-        <v>168</v>
-      </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4148,10 +4105,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4174,17 +4131,15 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4233,7 +4188,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4242,16 +4197,16 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AJ27" t="s" s="2">
-        <v>168</v>
-      </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-dmi-supplydelivery-entete-livraison.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplydelivery-entete-livraison.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:22:34+00:00</t>
+    <t>2026-03-05T10:23:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-supplydelivery-entete-livraison.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplydelivery-entete-livraison.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="261">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:23:55+00:00</t>
+    <t>2026-03-05T10:25:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -316,10 +316,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>SupplyDelivery.implicitRules</t>
   </si>
   <si>
@@ -339,6 +346,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>SupplyDelivery.language</t>
   </si>
   <si>
@@ -416,9 +426,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>SupplyDelivery.extension</t>
   </si>
   <si>
@@ -436,6 +443,9 @@
 </t>
   </si>
   <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
     <t>open</t>
   </si>
   <si>
@@ -462,10 +472,6 @@
     <t>Extension créée dans ce volet pour référencer l'organisation fabricant du DMI.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>SupplyDelivery.modifierExtension</t>
   </si>
   <si>
@@ -511,6 +517,9 @@
     <t>.id</t>
   </si>
   <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
     <t>SupplyDelivery.basedOn</t>
   </si>
   <si>
@@ -524,7 +533,14 @@
     <t>A plan, proposal or order that is fulfilled in whole or in part by this event.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -625,6 +641,9 @@
     <t>Indicates the type of dispensing event that is performed. Examples include: Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>The type of supply dispense.</t>
   </si>
   <si>
@@ -635,6 +654,9 @@
   </si>
   <si>
     <t>.code</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE</t>
   </si>
   <si>
     <t>SupplyDelivery.suppliedItem</t>
@@ -669,9 +691,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>SupplyDelivery.suppliedItem.extension</t>
   </si>
   <si>
@@ -714,7 +733,17 @@
     <t>The amount of supply that has been dispensed. Includes unit of measure.</t>
   </si>
   <si>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
+  </si>
+  <si>
     <t>.quantity</t>
+  </si>
+  <si>
+    <t>SN (see also Range) or CQ</t>
   </si>
   <si>
     <t>SupplyDelivery.suppliedItem.item[x]</t>
@@ -1136,7 +1165,7 @@
     <col min="26" max="26" width="43.90234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="30.5546875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1145,7 +1174,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="52.23046875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="27.45703125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="53.91015625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -1591,16 +1620,16 @@
         <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -1611,10 +1640,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1637,16 +1666,16 @@
         <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1696,7 +1725,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -1705,16 +1734,16 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -1725,10 +1754,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1751,16 +1780,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1786,13 +1815,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -1810,7 +1839,7 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -1819,16 +1848,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -1839,14 +1868,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -1865,16 +1894,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1924,7 +1953,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -1933,16 +1962,16 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -1953,14 +1982,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -1979,16 +2008,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2038,7 +2067,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2056,7 +2085,7 @@
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2067,10 +2096,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2093,13 +2122,13 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2138,17 +2167,19 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2157,10 +2188,10 @@
         <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2177,13 +2208,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>77</v>
@@ -2205,13 +2236,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2262,7 +2293,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2271,10 +2302,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2291,14 +2322,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2317,19 +2348,19 @@
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2366,19 +2397,19 @@
         <v>77</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2387,16 +2418,16 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2407,10 +2438,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2433,16 +2464,16 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2492,7 +2523,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2501,19 +2532,19 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>77</v>
@@ -2521,10 +2552,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2547,17 +2578,19 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O13" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -2606,7 +2639,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2615,19 +2648,19 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -2635,10 +2668,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2661,19 +2694,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -2722,7 +2755,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2731,19 +2764,19 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>77</v>
@@ -2751,10 +2784,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2777,16 +2810,16 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2812,31 +2845,31 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -2845,16 +2878,16 @@
         <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -2865,10 +2898,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2891,15 +2924,17 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -2948,7 +2983,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -2957,16 +2992,16 @@
         <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -2977,10 +3012,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3003,15 +3038,17 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3036,31 +3073,31 @@
         <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="Z17" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3069,19 +3106,19 @@
         <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>77</v>
+        <v>205</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3089,10 +3126,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3115,13 +3152,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3172,7 +3209,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3181,16 +3218,16 @@
         <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3201,10 +3238,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3227,13 +3264,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3284,7 +3321,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3302,7 +3339,7 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>209</v>
+        <v>108</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3313,14 +3350,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3339,16 +3376,16 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3386,19 +3423,19 @@
         <v>77</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3407,16 +3444,16 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>209</v>
+        <v>101</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3427,14 +3464,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3453,19 +3490,19 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -3514,7 +3551,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3523,16 +3560,16 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3543,10 +3580,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3569,15 +3606,17 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3626,7 +3665,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3635,19 +3674,19 @@
         <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>230</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -3655,10 +3694,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3681,13 +3720,13 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3738,7 +3777,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3747,16 +3786,16 @@
         <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -3767,10 +3806,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3793,16 +3832,16 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3852,7 +3891,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -3861,30 +3900,30 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3907,15 +3946,17 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -3964,7 +4005,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -3973,16 +4014,16 @@
         <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -3993,10 +4034,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4019,15 +4060,17 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4076,7 +4119,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4085,16 +4128,16 @@
         <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4105,10 +4148,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4131,15 +4174,17 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4188,7 +4233,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4197,16 +4242,16 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
